--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487052_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487052_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.502</v>
+        <v>2.9874</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1704</v>
+        <v>2.6291</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3316</v>
+        <v>0.3583</v>
       </c>
       <c r="G2" t="n">
         <v>3.214</v>
@@ -610,13 +610,13 @@
         <v>1.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1157</v>
+        <v>-0.6303</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4574</v>
+        <v>-0.0839</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.5463</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3684</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. UGARTE JAUREGUI</t>
+          <t>M. CARCOBA BEDIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5147</v>
+        <v>1.0075</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3986</v>
+        <v>-0.5788</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1161</v>
+        <v>1.5863</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2049</v>
+        <v>1.0421</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.472</v>
+        <v>1.6819</v>
       </c>
       <c r="I3" t="n">
-        <v>0.267</v>
+        <v>-0.6398</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.6521</v>
+        <v>-0.5805</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6521</v>
+        <v>0.714</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-1.2945</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4472</v>
+        <v>1.6226</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1801</v>
+        <v>0.9679</v>
       </c>
       <c r="O3" t="n">
-        <v>0.267</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.386</v>
+        <v>0.193</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R3" t="n">
-        <v>0.386</v>
+        <v>1.158</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6617</v>
+        <v>0.3863</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7649</v>
+        <v>0.6808</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1031</v>
+        <v>-0.2945</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3281</v>
+        <v>-0.614</v>
       </c>
       <c r="W3" t="n">
         <v>0.2859</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.614</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. CARCOBA BEDIA</t>
+          <t>J. UGARTE JAUREGUI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6978</v>
+        <v>0.4973</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3989</v>
+        <v>0.1161</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0421</v>
+        <v>-0.2049</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6819</v>
+        <v>-0.472</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6398</v>
+        <v>0.267</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5805</v>
+        <v>-0.6521</v>
       </c>
       <c r="K4" t="n">
-        <v>0.714</v>
+        <v>-0.6521</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2945</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.6226</v>
+        <v>0.4472</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9679</v>
+        <v>0.1801</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.267</v>
       </c>
       <c r="P4" t="n">
-        <v>0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="S4" t="n">
-        <v>0.08</v>
+        <v>0.7605</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5619</v>
+        <v>0.8636</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4819</v>
+        <v>-0.1031</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.614</v>
+        <v>-0.3281</v>
       </c>
       <c r="W4" t="n">
         <v>0.2859</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8999</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. MARTINEZ FERNANDEZ</t>
+          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.556</v>
+        <v>0.3082</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.3944</v>
+        <v>-2.1667</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9504</v>
+        <v>2.475</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3752</v>
+        <v>3.0864</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7215</v>
+        <v>4.5829</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0968</v>
+        <v>-1.4966</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3439</v>
+        <v>3.0644</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1811</v>
+        <v>3.3014</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1628</v>
+        <v>-0.237</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7191</v>
+        <v>0.022</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5404</v>
+        <v>1.2815</v>
       </c>
       <c r="O5" t="n">
         <v>-1.2596</v>
       </c>
       <c r="P5" t="n">
-        <v>0.772</v>
+        <v>-2.8951</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1231</v>
+        <v>-5.9833</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8951</v>
+        <v>3.0881</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1838</v>
+        <v>-0.4145</v>
       </c>
       <c r="T5" t="n">
-        <v>0.041</v>
+        <v>-0.4336</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1428</v>
+        <v>0.0191</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0246</v>
+        <v>0.5315</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6562</v>
+        <v>1.1857</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3684</v>
+        <v>-0.6543</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GOMEZ MERODIO</t>
+          <t>S. MARTINEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0563</v>
+        <v>-0.1886</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0028</v>
+        <v>-2.4163</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0535</v>
+        <v>2.2276</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.3752</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1708</v>
+        <v>0.7215</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4134</v>
+        <v>-1.0968</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0105</v>
+        <v>0.3439</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0105</v>
+        <v>0.1811</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.1628</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5738</v>
+        <v>-0.7191</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1604</v>
+        <v>0.5404</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4134</v>
+        <v>-1.2596</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.386</v>
+        <v>0.772</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.965</v>
+        <v>-2.1231</v>
       </c>
       <c r="R6" t="n">
-        <v>0.579</v>
+        <v>2.8951</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0265</v>
+        <v>0.4392</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.0192</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0482</v>
+        <v>0.42</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.0246</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3684</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
+          <t>J. GOMEZ MERODIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4036</v>
+        <v>-0.3175</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.1463</v>
+        <v>-0.3978</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7426</v>
+        <v>0.0803</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0864</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5829</v>
+        <v>-0.1708</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4966</v>
+        <v>-0.4134</v>
       </c>
       <c r="J7" t="n">
-        <v>3.0644</v>
+        <v>-0.0105</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3014</v>
+        <v>-0.0105</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.237</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.022</v>
+        <v>-0.5738</v>
       </c>
       <c r="N7" t="n">
-        <v>1.2815</v>
+        <v>-0.1604</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2596</v>
+        <v>-0.4134</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.8951</v>
+        <v>-0.386</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.9833</v>
+        <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>3.0881</v>
+        <v>0.579</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1263</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.4132</v>
+        <v>0.5777</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2868</v>
+        <v>0.075</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5315</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1857</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4082</v>
+        <v>-1.5024</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.175</v>
+        <v>-4.6975</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7668</v>
+        <v>3.1951</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7847</v>
@@ -1156,13 +1156,13 @@
         <v>2.7021</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2948</v>
+        <v>-0.389</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5750999999999999</v>
+        <v>0.0526</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8699</v>
+        <v>-0.4416</v>
       </c>
       <c r="V9" t="n">
         <v>2.9874</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9436</v>
+        <v>-1.8633</v>
       </c>
       <c r="E10" t="n">
         <v>-1.7697</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1739</v>
+        <v>-0.0936</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9131</v>
@@ -1234,13 +1234,13 @@
         <v>0.193</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2584</v>
+        <v>-0.1781</v>
       </c>
       <c r="T10" t="n">
         <v>-0.1785</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.08</v>
+        <v>0.0003</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5226</v>
+        <v>-2.3407</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.468</v>
+        <v>-2.6074</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0546</v>
+        <v>0.2666</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5718</v>
@@ -1312,13 +1312,13 @@
         <v>1.9301</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3894</v>
+        <v>-0.2076</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7588</v>
+        <v>0.1018</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6306</v>
+        <v>-0.3094</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3684</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8736</v>
+        <v>-3.6333</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.9049</v>
+        <v>-3.5842</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0313</v>
+        <v>-0.049</v>
       </c>
       <c r="G12" t="n">
         <v>-2.2278</v>
@@ -1390,13 +1390,13 @@
         <v>1.5441</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2103</v>
+        <v>0.0301</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9373</v>
+        <v>0.3834</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.273</v>
+        <v>-0.3533</v>
       </c>
       <c r="V12" t="n">
         <v>-0.08450000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.2285</v>
+        <v>-5.3363</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.9843</v>
+        <v>-15.092</v>
       </c>
       <c r="F13" t="n">
-        <v>9.755699999999999</v>
+        <v>9.755700000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-0.7262</v>
@@ -1453,7 +1453,7 @@
         <v>0.6111</v>
       </c>
       <c r="N13" t="n">
-        <v>6.273300000000001</v>
+        <v>6.273299999999999</v>
       </c>
       <c r="O13" t="n">
         <v>-5.6625</v>
@@ -1468,10 +1468,10 @@
         <v>16.4056</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4428999999999998</v>
+        <v>0.4492999999999998</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0908</v>
+        <v>1.9831</v>
       </c>
       <c r="U13" t="n">
         <v>-1.5338</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4266</v>
+        <v>7.1877</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0885</v>
+        <v>4.6893</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3381</v>
+        <v>2.4984</v>
       </c>
       <c r="G14" t="n">
         <v>1.9747</v>
@@ -1546,13 +1546,13 @@
         <v>3.4741</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1098</v>
+        <v>-0.3487</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4931</v>
+        <v>0.1078</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6167</v>
+        <v>-0.4565</v>
       </c>
       <c r="V14" t="n">
         <v>2.0875</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2707</v>
+        <v>2.8499</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1201</v>
+        <v>-0.3806</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1506</v>
+        <v>3.2305</v>
       </c>
       <c r="G15" t="n">
         <v>1.7028</v>
@@ -1624,13 +1624,13 @@
         <v>2.5091</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0238</v>
+        <v>-0.3969</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5169</v>
+        <v>0.0162</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4931</v>
+        <v>-0.4131</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. URTXULUTEGI NAVARRI</t>
+          <t>E. HUIZI ZUBELDIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4845</v>
+        <v>2.1621</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7151</v>
+        <v>0.1269</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2305</v>
+        <v>2.0351</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9439</v>
+        <v>1.6989</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0568</v>
+        <v>-0.5703</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8871</v>
+        <v>2.2692</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8449</v>
+        <v>1.9188</v>
       </c>
       <c r="K16" t="n">
-        <v>2.339</v>
+        <v>0.6985</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5059</v>
+        <v>1.2203</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9009</v>
+        <v>-0.2199</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2822</v>
+        <v>-1.2688</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3813</v>
+        <v>1.0489</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.772</v>
+        <v>0.579</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1231</v>
+        <v>2.5091</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6471</v>
+        <v>0.8242</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4627</v>
+        <v>0.1382</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1844</v>
+        <v>0.6861</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.0403</v>
+        <v>-0.9401</v>
       </c>
       <c r="W16" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2682</v>
+        <v>-0.9401</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. HUIZI ZUBELDIA</t>
+          <t>J. URTXULUTEGI NAVARRI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4554</v>
+        <v>1.8381</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8745000000000001</v>
+        <v>2.0155</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3299</v>
+        <v>-0.1773</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6989</v>
+        <v>2.9439</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5703</v>
+        <v>1.0568</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2692</v>
+        <v>1.8871</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9188</v>
+        <v>3.8449</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6985</v>
+        <v>2.339</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2203</v>
+        <v>1.5059</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2199</v>
+        <v>-0.9009</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2688</v>
+        <v>-1.2822</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0489</v>
+        <v>0.3813</v>
       </c>
       <c r="P17" t="n">
-        <v>0.579</v>
+        <v>-0.772</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5091</v>
+        <v>2.1231</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1176</v>
+        <v>-0.2935</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8632</v>
+        <v>-0.1622</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9809</v>
+        <v>-0.1312</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9401</v>
+        <v>-0.0403</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9401</v>
+        <v>-1.2682</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. IRASTORZA EZKIAGA</t>
+          <t>J. ELOSEGUI OLANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.353</v>
+        <v>0.6857</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0776</v>
+        <v>-1.4261</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4305</v>
+        <v>2.1119</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6355</v>
+        <v>0.0146</v>
       </c>
       <c r="H18" t="n">
-        <v>0.502</v>
+        <v>-0.8807</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1335</v>
+        <v>0.8954</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0414</v>
+        <v>-0.4191</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0414</v>
+        <v>0.0207</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.4398</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5941</v>
+        <v>0.4338</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4606</v>
+        <v>-0.9014</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1335</v>
+        <v>1.3352</v>
       </c>
       <c r="P18" t="n">
-        <v>0.772</v>
+        <v>0.386</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R18" t="n">
-        <v>0.772</v>
+        <v>1.3511</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7687</v>
+        <v>-0.0853</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.119</v>
+        <v>-0.042</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6498</v>
+        <v>-0.0433</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2859</v>
+        <v>0.3704</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2859</v>
+        <v>0.3704</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. ELOSEGUI OLANO</t>
+          <t>A. IRASTORZA EZKIAGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1715</v>
+        <v>0.4799</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7265</v>
+        <v>0.0226</v>
       </c>
       <c r="F19" t="n">
-        <v>1.898</v>
+        <v>0.4573</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0146</v>
+        <v>0.6355</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8807</v>
+        <v>0.502</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8954</v>
+        <v>0.1335</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4191</v>
+        <v>0.0414</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0207</v>
+        <v>0.0414</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4398</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4338</v>
+        <v>0.5941</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9014</v>
+        <v>0.4606</v>
       </c>
       <c r="O19" t="n">
-        <v>1.3352</v>
+        <v>0.1335</v>
       </c>
       <c r="P19" t="n">
-        <v>0.386</v>
+        <v>0.772</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3511</v>
+        <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5995</v>
+        <v>-0.6418</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3424</v>
+        <v>-0.0188</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2571</v>
+        <v>-0.623</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3704</v>
+        <v>-0.2859</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3704</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. ETXEBERRIA AGUIRREZABALA</t>
+          <t>A. ALDA IRAOLA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0804</v>
+        <v>0.1419</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4035</v>
+        <v>-2.0063</v>
       </c>
       <c r="F20" t="n">
-        <v>2.3231</v>
+        <v>2.1482</v>
       </c>
       <c r="G20" t="n">
-        <v>-6.2477</v>
+        <v>0.6875</v>
       </c>
       <c r="H20" t="n">
-        <v>-6.9317</v>
+        <v>-0.1315</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.8872</v>
+        <v>0.0398</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.3824</v>
+        <v>0.0155</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5048</v>
+        <v>0.0243</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3604</v>
+        <v>0.6478</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5493</v>
+        <v>-0.1469</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1888</v>
+        <v>0.7947</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.772</v>
+        <v>-0.386</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1231</v>
+        <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>6.0395</v>
+        <v>-0.1596</v>
       </c>
       <c r="T20" t="n">
-        <v>4.9073</v>
+        <v>-0.116</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1322</v>
+        <v>-0.0436</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8999</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4716</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ALDA IRAOLA</t>
+          <t>A. ARMENDARIZ LOPEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3727</v>
+        <v>-0.7991</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3067</v>
+        <v>-1.01</v>
       </c>
       <c r="F21" t="n">
-        <v>1.934</v>
+        <v>0.2109</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6875</v>
+        <v>-0.1218</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1315</v>
+        <v>-1.6177</v>
       </c>
       <c r="I21" t="n">
-        <v>0.819</v>
+        <v>1.4959</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0398</v>
+        <v>-0.0757</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0155</v>
+        <v>-1.1903</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0243</v>
+        <v>1.1146</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6478</v>
+        <v>-0.0461</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1469</v>
+        <v>-0.4274</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7947</v>
+        <v>0.3813</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.386</v>
+        <v>1.158</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5441</v>
+        <v>2.1231</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6742</v>
+        <v>0.0469</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4164</v>
+        <v>0.0308</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2578</v>
+        <v>0.0162</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.8822</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.8822</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ARMENDARIZ LOPEZ</t>
+          <t>A. GORDILLO BELTRAN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.394</v>
+        <v>-1.1625</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3104</v>
+        <v>-3.6308</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.08359999999999999</v>
+        <v>2.4682</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1218</v>
+        <v>-1.1907</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6177</v>
+        <v>-1.4792</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4959</v>
+        <v>0.2885</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0757</v>
+        <v>-1.6052</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1903</v>
+        <v>-1.6459</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1146</v>
+        <v>0.0407</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0461</v>
+        <v>0.4145</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4274</v>
+        <v>0.1667</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3813</v>
+        <v>0.2478</v>
       </c>
       <c r="P22" t="n">
-        <v>1.158</v>
+        <v>0.772</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1231</v>
+        <v>2.7021</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.3754</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2697</v>
+        <v>-0.0955</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2783</v>
+        <v>-0.28</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8822</v>
+        <v>-0.3684</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.8822</v>
+        <v>-0.3684</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. GORDILLO BELTRAN</t>
+          <t>U. CONDE LAKUNTZA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1441</v>
+        <v>-2.6009</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.532</v>
+        <v>-2.348</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3879</v>
+        <v>-0.253</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.1907</v>
+        <v>-1.3715</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4792</v>
+        <v>0.0694</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2885</v>
+        <v>-1.4409</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.6052</v>
+        <v>-0.5907</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.6459</v>
+        <v>0.7038</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0407</v>
+        <v>-1.2945</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4145</v>
+        <v>-0.7808</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1667</v>
+        <v>-0.6344</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2478</v>
+        <v>-0.1464</v>
       </c>
       <c r="P23" t="n">
-        <v>0.772</v>
+        <v>-0.965</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7021</v>
+        <v>0.965</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.357</v>
+        <v>0.3074</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9967</v>
+        <v>0.1729</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3603</v>
+        <v>0.1345</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3684</v>
+        <v>-0.5717</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3684</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>U. CONDE LAKUNTZA</t>
+          <t>B. ETXEBERRIA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.942</v>
+        <v>-3.8867</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4481</v>
+        <v>-5.8083</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4939</v>
+        <v>1.9216</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.3715</v>
+        <v>-6.2477</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0694</v>
+        <v>-6.9317</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4409</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5907</v>
+        <v>-5.8872</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7038</v>
+        <v>-5.3824</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2945</v>
+        <v>-0.5048</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7808</v>
+        <v>-0.3604</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6344</v>
+        <v>-1.5493</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1464</v>
+        <v>1.1888</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.965</v>
+        <v>-0.772</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R24" t="n">
-        <v>0.965</v>
+        <v>2.1231</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0337</v>
+        <v>2.2332</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0727</v>
+        <v>1.5025</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1064</v>
+        <v>0.7307</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5717</v>
+        <v>0.8999</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.4716</v>
       </c>
       <c r="X24" t="n">
         <v>-0.5717</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.2285</v>
+        <v>6.896100000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.755600000000001</v>
+        <v>-9.755800000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>15.9841</v>
+        <v>16.6518</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7261999999999997</v>
+        <v>0.7261999999999995</v>
       </c>
       <c r="H25" t="n">
         <v>-14.1539</v>
@@ -2377,13 +2377,13 @@
         <v>14.8803</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6109000000000007</v>
+        <v>-0.6109</v>
       </c>
       <c r="K25" t="n">
         <v>-6.273299999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>5.6625</v>
+        <v>5.662499999999999</v>
       </c>
       <c r="M25" t="n">
         <v>1.3375</v>
@@ -2404,16 +2404,16 @@
         <v>22.19590000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4430000000000006</v>
+        <v>1.1105</v>
       </c>
       <c r="T25" t="n">
-        <v>1.5337</v>
+        <v>1.5339</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0908</v>
+        <v>-0.4231999999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.7308000000000001</v>
+        <v>-0.7308</v>
       </c>
       <c r="W25" t="n">
         <v>5.7273</v>
